--- a/doc/ConexionesRiego_v1_0.xlsx
+++ b/doc/ConexionesRiego_v1_0.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9fd291838b10efa6/Documentos/GitHub/2526CL13_Riego_offlinev1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9fd291838b10efa6/Documentos/GitHub/2526CL13_Riego_offlinev1/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="163" documentId="8_{2EE8251E-253A-438C-AC51-A1BAD384CA53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{53DC3E4B-8F08-4986-8A99-9BA12D720103}"/>
+  <xr:revisionPtr revIDLastSave="201" documentId="8_{2EE8251E-253A-438C-AC51-A1BAD384CA53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D42BEE4A-2D63-4BAA-96AA-25E18F37F462}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{10D26D02-5518-4F3E-8C32-499B77D2AAB5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{10D26D02-5518-4F3E-8C32-499B77D2AAB5}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="75">
   <si>
     <t>Pin Proto</t>
   </si>
@@ -286,12 +286,45 @@
   <si>
     <t>Pulsador en eje Rotray encoder + anti-rebotes x HW</t>
   </si>
+  <si>
+    <t>Configuracion de Pines en uPy</t>
+  </si>
+  <si>
+    <t>CONFIRM = 18
+BACK = 19
+PUSH = 20
+# 0.1 Creacion 3 pulsadores 
+confPul = Pin(CONFIRM, Pin.IN) # pull up por circuito
+backPul = Pin(BACK, Pin.IN) # pull up por circuito
+pushPul = Pin(PUSH, Pin.IN) # pull up por circuito</t>
+  </si>
+  <si>
+    <t>alimentaSensor = machine.Pin(21, machine.Pin.OUT)</t>
+  </si>
+  <si>
+    <t>sensoHumSuelo = machine.ADC(0) # ADCO or GPIO26</t>
+  </si>
+  <si>
+    <t>sensorWTank = Pin(22, Pin.IN)</t>
+  </si>
+  <si>
+    <t>En modo entrada digital</t>
+  </si>
+  <si>
+    <t>MOTORPIN = 15
+pwmMotor = PWM(Pin(MOTORPIN))
+pwmMotor.freq(1000)</t>
+  </si>
+  <si>
+    <t>FREQ = 400_000   # lowering this value in case of "Errno 5"
+i2c = I2C(0, sda = Pin(4), scl = Pin(5), freq = FREQ)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -331,6 +364,20 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -501,10 +548,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="medium">
+      <right style="thin">
         <color indexed="64"/>
       </right>
       <top style="thin">
@@ -514,21 +561,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
+      <right style="thin">
         <color indexed="64"/>
       </right>
       <top/>
@@ -541,24 +577,22 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="medium">
+      <right style="thin">
         <color indexed="64"/>
       </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
+      <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
+      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -566,12 +600,19 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
+      <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
       <top/>
       <bottom style="thin">
         <color indexed="64"/>
@@ -582,13 +623,11 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
+      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -597,9 +636,7 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
+      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -612,83 +649,34 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -706,68 +694,144 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -786,6 +850,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1105,356 +1173,400 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCF6ACB7-3C61-475F-AE9E-E0F1AA80F7E8}">
-  <dimension ref="A1:E27"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:F27"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12.36328125" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="20.36328125" customWidth="1"/>
-    <col min="5" max="5" width="33.26953125" customWidth="1"/>
+    <col min="4" max="4" width="20.42578125" customWidth="1"/>
+    <col min="5" max="5" width="33.28515625" customWidth="1"/>
+    <col min="6" max="6" width="42.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="2">
         <v>46160</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="4" spans="1:5" ht="37" x14ac:dyDescent="0.35">
-      <c r="A4" s="32" t="s">
+    <row r="3" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:6" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A4" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="33" t="s">
+      <c r="B4" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="34" t="s">
+      <c r="C4" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="34" t="s">
+      <c r="D4" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="35" t="s">
+      <c r="E4" s="18" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" ht="18.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="36" t="s">
+      <c r="F4" s="18" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="37" t="s">
+      <c r="E5" s="50" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="36" t="s">
+      <c r="F5" s="71" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="10"/>
-      <c r="E6" s="38"/>
-    </row>
-    <row r="7" spans="1:5" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="36" t="s">
+      <c r="D6" s="41"/>
+      <c r="E6" s="51"/>
+      <c r="F6" s="69"/>
+    </row>
+    <row r="7" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="10"/>
-      <c r="E7" s="38"/>
-    </row>
-    <row r="8" spans="1:5" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A8" s="39"/>
-      <c r="B8" s="11" t="s">
+      <c r="D7" s="41"/>
+      <c r="E7" s="51"/>
+      <c r="F7" s="69"/>
+    </row>
+    <row r="8" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A8" s="20"/>
+      <c r="B8" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="10"/>
-      <c r="E8" s="40"/>
-    </row>
-    <row r="9" spans="1:5" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A9" s="36" t="s">
+      <c r="D8" s="41"/>
+      <c r="E8" s="52"/>
+      <c r="F8" s="70"/>
+    </row>
+    <row r="9" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A9" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="10"/>
-      <c r="E9" s="41" t="s">
+      <c r="D9" s="41"/>
+      <c r="E9" s="53" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A10" s="36" t="s">
+      <c r="F9" s="65"/>
+    </row>
+    <row r="10" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A10" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="10"/>
-      <c r="E10" s="41" t="s">
+      <c r="D10" s="41"/>
+      <c r="E10" s="53" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A11" s="36" t="s">
+      <c r="F10" s="65"/>
+    </row>
+    <row r="11" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="D11" s="10"/>
-      <c r="E11" s="41" t="s">
+      <c r="D11" s="41"/>
+      <c r="E11" s="53" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A12" s="36" t="s">
+      <c r="F11" s="66" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A12" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="D12" s="10"/>
-      <c r="E12" s="41" t="s">
+      <c r="D12" s="41"/>
+      <c r="E12" s="53" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" ht="37" x14ac:dyDescent="0.45">
-      <c r="A13" s="36" t="s">
+      <c r="F12" s="67"/>
+    </row>
+    <row r="13" spans="1:6" ht="37.5" x14ac:dyDescent="0.3">
+      <c r="A13" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="D13" s="12"/>
-      <c r="E13" s="65" t="s">
+      <c r="D13" s="42"/>
+      <c r="E13" s="54" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A14" s="42" t="s">
+      <c r="F13" s="68"/>
+    </row>
+    <row r="14" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A14" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="D14" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="E14" s="43"/>
-    </row>
-    <row r="15" spans="1:5" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A15" s="42"/>
-      <c r="B15" s="13" t="s">
+      <c r="E14" s="55"/>
+      <c r="F14" s="65"/>
+    </row>
+    <row r="15" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A15" s="21"/>
+      <c r="B15" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="C15" s="14" t="s">
+      <c r="C15" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D15" s="16"/>
-      <c r="E15" s="43"/>
-    </row>
-    <row r="16" spans="1:5" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A16" s="42"/>
-      <c r="B16" s="13" t="s">
+      <c r="D15" s="44"/>
+      <c r="E15" s="55"/>
+      <c r="F15" s="65"/>
+    </row>
+    <row r="16" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A16" s="21"/>
+      <c r="B16" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="C16" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D16" s="17"/>
-      <c r="E16" s="43"/>
-    </row>
-    <row r="17" spans="1:5" ht="37" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="44" t="s">
+      <c r="D16" s="45"/>
+      <c r="E16" s="55"/>
+      <c r="F16" s="65"/>
+    </row>
+    <row r="17" spans="1:6" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="23" t="s">
+      <c r="B17" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="C17" s="18" t="s">
+      <c r="C17" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="D17" s="19" t="s">
+      <c r="D17" s="47" t="s">
         <v>32</v>
       </c>
-      <c r="E17" s="45" t="s">
+      <c r="E17" s="56" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A18" s="46"/>
-      <c r="B18" s="21" t="s">
+      <c r="F17" s="72" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A18" s="23"/>
+      <c r="B18" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="C18" s="18" t="s">
+      <c r="C18" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D18" s="20"/>
-      <c r="E18" s="47"/>
-    </row>
-    <row r="19" spans="1:5" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A19" s="48" t="s">
+      <c r="D18" s="48"/>
+      <c r="E18" s="57"/>
+      <c r="F18" s="73"/>
+    </row>
+    <row r="19" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A19" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="C19" s="21" t="s">
+      <c r="C19" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D19" s="22"/>
-      <c r="E19" s="49" t="s">
+      <c r="D19" s="49"/>
+      <c r="E19" s="58" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A20" s="50"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="24" t="s">
+      <c r="F19" s="72" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A20" s="37"/>
+      <c r="B20" s="35"/>
+      <c r="C20" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="D20" s="25" t="s">
+      <c r="D20" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="E20" s="51"/>
-    </row>
-    <row r="21" spans="1:5" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A21" s="52"/>
-      <c r="B21" s="24" t="s">
+      <c r="E20" s="59"/>
+      <c r="F20" s="73"/>
+    </row>
+    <row r="21" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A21" s="24"/>
+      <c r="B21" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="C21" s="26" t="s">
+      <c r="C21" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="D21" s="27"/>
-      <c r="E21" s="53"/>
-    </row>
-    <row r="22" spans="1:5" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A22" s="52" t="s">
+      <c r="D21" s="32"/>
+      <c r="E21" s="60"/>
+      <c r="F21" s="65"/>
+    </row>
+    <row r="22" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A22" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="B22" s="24" t="s">
+      <c r="B22" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="C22" s="26" t="s">
+      <c r="C22" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="D22" s="28"/>
-      <c r="E22" s="53"/>
-    </row>
-    <row r="23" spans="1:5" ht="55.5" x14ac:dyDescent="0.45">
-      <c r="A23" s="54" t="s">
+      <c r="D22" s="33"/>
+      <c r="E22" s="60" t="s">
+        <v>72</v>
+      </c>
+      <c r="F22" s="65" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="56.25" x14ac:dyDescent="0.3">
+      <c r="A23" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="B23" s="29" t="s">
+      <c r="B23" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C23" s="63" t="s">
+      <c r="C23" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="D23" s="30" t="s">
+      <c r="D23" s="38" t="s">
         <v>59</v>
       </c>
-      <c r="E23" s="55"/>
-    </row>
-    <row r="24" spans="1:5" ht="18.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A24" s="54" t="s">
+      <c r="E23" s="61"/>
+      <c r="F23" s="74" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="B24" s="31" t="s">
+      <c r="B24" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="C24" s="63" t="s">
+      <c r="C24" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="D24" s="30"/>
-      <c r="E24" s="56"/>
-    </row>
-    <row r="25" spans="1:5" ht="37" x14ac:dyDescent="0.45">
-      <c r="A25" s="61"/>
-      <c r="B25" s="62"/>
-      <c r="C25" s="63" t="s">
+      <c r="D24" s="38"/>
+      <c r="E24" s="62"/>
+      <c r="F24" s="65"/>
+    </row>
+    <row r="25" spans="1:6" ht="37.5" x14ac:dyDescent="0.3">
+      <c r="A25" s="27"/>
+      <c r="B25" s="28"/>
+      <c r="C25" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="D25" s="30"/>
-      <c r="E25" s="57" t="s">
+      <c r="D25" s="38"/>
+      <c r="E25" s="63" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A26" s="54" t="s">
+      <c r="F25" s="65"/>
+    </row>
+    <row r="26" spans="1:6" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="B26" s="58" t="s">
+      <c r="B26" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="C26" s="64" t="s">
+      <c r="C26" s="30" t="s">
         <v>51</v>
       </c>
-      <c r="D26" s="59"/>
-      <c r="E26" s="60" t="s">
+      <c r="D26" s="39"/>
+      <c r="E26" s="64" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="6"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
+      <c r="F26" s="65"/>
+    </row>
+    <row r="27" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="14">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="D17:D19"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="F11:F13"/>
+    <mergeCell ref="F5:F8"/>
+    <mergeCell ref="F17:F18"/>
+    <mergeCell ref="F19:F20"/>
     <mergeCell ref="D20:D22"/>
     <mergeCell ref="B19:B20"/>
     <mergeCell ref="A19:A20"/>
@@ -1462,9 +1574,6 @@
     <mergeCell ref="E5:E8"/>
     <mergeCell ref="D5:D13"/>
     <mergeCell ref="D14:D16"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="D17:D19"/>
-    <mergeCell ref="E19:E20"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/doc/ConexionesRiego_v1_0.xlsx
+++ b/doc/ConexionesRiego_v1_0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9fd291838b10efa6/Documentos/GitHub/2526CL13_Riego_offlinev1/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="201" documentId="8_{2EE8251E-253A-438C-AC51-A1BAD384CA53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D42BEE4A-2D63-4BAA-96AA-25E18F37F462}"/>
+  <xr:revisionPtr revIDLastSave="229" documentId="8_{2EE8251E-253A-438C-AC51-A1BAD384CA53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{004F016C-9D9A-4A35-801D-CD827CFA05BA}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{10D26D02-5518-4F3E-8C32-499B77D2AAB5}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{10D26D02-5518-4F3E-8C32-499B77D2AAB5}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="83">
   <si>
     <t>Pin Proto</t>
   </si>
@@ -156,9 +156,6 @@
   </si>
   <si>
     <t>DER - 15</t>
-  </si>
-  <si>
-    <t>Sensor Humedad Tanque agua</t>
   </si>
   <si>
     <t>Digital Out</t>
@@ -318,6 +315,33 @@
   <si>
     <t>FREQ = 400_000   # lowering this value in case of "Errno 5"
 i2c = I2C(0, sda = Pin(4), scl = Pin(5), freq = FREQ)</t>
+  </si>
+  <si>
+    <t>Sensor Resistivo Humedad Tanque agua</t>
+  </si>
+  <si>
+    <t>Sensor Flotador Tanque agua</t>
+  </si>
+  <si>
+    <t>GPIO01</t>
+  </si>
+  <si>
+    <t>IZQ-2</t>
+  </si>
+  <si>
+    <t>IZQ-3</t>
+  </si>
+  <si>
+    <t>SF1</t>
+  </si>
+  <si>
+    <t>Es como un pulsador: se pueden invertir los cables sin consecuencias</t>
+  </si>
+  <si>
+    <t>En el progrma hay que invertir la logica de Tanque lleno y vacio al leer el pin ( ver 8.1 y siguientes)</t>
+  </si>
+  <si>
+    <t>1' Tank Empty / '0' Tank FULL ( ver 7.1)</t>
   </si>
 </sst>
 </file>
@@ -383,7 +407,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -426,6 +450,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="17">
     <border>
@@ -649,7 +679,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -715,72 +745,6 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -790,12 +754,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
@@ -806,6 +764,84 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -815,23 +851,41 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1173,35 +1227,35 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCF6ACB7-3C61-475F-AE9E-E0F1AA80F7E8}">
-  <dimension ref="A1:F27"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F29"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="12.42578125" customWidth="1"/>
+    <col min="2" max="2" width="12.453125" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="20.42578125" customWidth="1"/>
-    <col min="5" max="5" width="33.28515625" customWidth="1"/>
-    <col min="6" max="6" width="42.42578125" customWidth="1"/>
+    <col min="4" max="4" width="20.453125" customWidth="1"/>
+    <col min="5" max="5" width="33.26953125" customWidth="1"/>
+    <col min="6" max="6" width="42.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="46" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" s="64" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>31</v>
       </c>
       <c r="B2" s="2">
-        <v>46160</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="1:6" ht="37.5" x14ac:dyDescent="0.25">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="4" spans="1:6" ht="37" x14ac:dyDescent="0.35">
       <c r="A4" s="15" t="s">
         <v>19</v>
       </c>
@@ -1218,10 +1272,10 @@
         <v>2</v>
       </c>
       <c r="F4" s="18" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="19" t="s">
         <v>16</v>
       </c>
@@ -1231,17 +1285,17 @@
       <c r="C5" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="40" t="s">
+      <c r="D5" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="50" t="s">
+      <c r="E5" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="71" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="F5" s="73" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A6" s="19" t="s">
         <v>17</v>
       </c>
@@ -1251,11 +1305,11 @@
       <c r="C6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="41"/>
-      <c r="E6" s="51"/>
-      <c r="F6" s="69"/>
-    </row>
-    <row r="7" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="D6" s="55"/>
+      <c r="E6" s="52"/>
+      <c r="F6" s="74"/>
+    </row>
+    <row r="7" spans="1:6" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A7" s="19" t="s">
         <v>18</v>
       </c>
@@ -1265,23 +1319,23 @@
       <c r="C7" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="41"/>
-      <c r="E7" s="51"/>
-      <c r="F7" s="69"/>
-    </row>
-    <row r="8" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="D7" s="55"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="74"/>
+    </row>
+    <row r="8" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A8" s="20"/>
       <c r="B8" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="41"/>
-      <c r="E8" s="52"/>
-      <c r="F8" s="70"/>
-    </row>
-    <row r="9" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="D8" s="55"/>
+      <c r="E8" s="53"/>
+      <c r="F8" s="75"/>
+    </row>
+    <row r="9" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A9" s="19" t="s">
         <v>20</v>
       </c>
@@ -1291,13 +1345,13 @@
       <c r="C9" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="41"/>
-      <c r="E9" s="53" t="s">
+      <c r="D9" s="55"/>
+      <c r="E9" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="65"/>
-    </row>
-    <row r="10" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="F9" s="41"/>
+    </row>
+    <row r="10" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A10" s="19" t="s">
         <v>21</v>
       </c>
@@ -1307,47 +1361,47 @@
       <c r="C10" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="41"/>
-      <c r="E10" s="53" t="s">
+      <c r="D10" s="55"/>
+      <c r="E10" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="F10" s="65"/>
-    </row>
-    <row r="11" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F10" s="41"/>
+    </row>
+    <row r="11" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="19" t="s">
         <v>22</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D11" s="41"/>
-      <c r="E11" s="53" t="s">
-        <v>65</v>
-      </c>
-      <c r="F11" s="66" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+        <v>59</v>
+      </c>
+      <c r="D11" s="55"/>
+      <c r="E11" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="F11" s="70" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A12" s="19" t="s">
         <v>23</v>
       </c>
       <c r="B12" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D12" s="55"/>
+      <c r="E12" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="C12" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D12" s="41"/>
-      <c r="E12" s="53" t="s">
-        <v>65</v>
-      </c>
-      <c r="F12" s="67"/>
-    </row>
-    <row r="13" spans="1:6" ht="37.5" x14ac:dyDescent="0.3">
+      <c r="F12" s="71"/>
+    </row>
+    <row r="13" spans="1:6" ht="37" x14ac:dyDescent="0.45">
       <c r="A13" s="19" t="s">
         <v>24</v>
       </c>
@@ -1355,211 +1409,247 @@
         <v>37</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="D13" s="42"/>
-      <c r="E13" s="54" t="s">
-        <v>66</v>
-      </c>
-      <c r="F13" s="68"/>
-    </row>
-    <row r="14" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+        <v>61</v>
+      </c>
+      <c r="D13" s="56"/>
+      <c r="E13" s="32" t="s">
+        <v>65</v>
+      </c>
+      <c r="F13" s="72"/>
+    </row>
+    <row r="14" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A14" s="21" t="s">
         <v>29</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="43" t="s">
+      <c r="D14" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="E14" s="55"/>
-      <c r="F14" s="65"/>
-    </row>
-    <row r="15" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="E14" s="33"/>
+      <c r="F14" s="41"/>
+    </row>
+    <row r="15" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A15" s="21"/>
       <c r="B15" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D15" s="44"/>
-      <c r="E15" s="55"/>
-      <c r="F15" s="65"/>
-    </row>
-    <row r="16" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="D15" s="58"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="41"/>
+    </row>
+    <row r="16" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A16" s="21"/>
       <c r="B16" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D16" s="45"/>
-      <c r="E16" s="55"/>
-      <c r="F16" s="65"/>
-    </row>
-    <row r="17" spans="1:6" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D16" s="59"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="41"/>
+    </row>
+    <row r="17" spans="1:6" ht="37" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="22" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="D17" s="47" t="s">
+      <c r="D17" s="65" t="s">
         <v>32</v>
       </c>
-      <c r="E17" s="56" t="s">
-        <v>43</v>
-      </c>
-      <c r="F17" s="72" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="E17" s="34" t="s">
+        <v>42</v>
+      </c>
+      <c r="F17" s="76" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A18" s="23"/>
       <c r="B18" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C18" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D18" s="48"/>
-      <c r="E18" s="57"/>
-      <c r="F18" s="73"/>
-    </row>
-    <row r="19" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A19" s="36" t="s">
+      <c r="D18" s="66"/>
+      <c r="E18" s="35"/>
+      <c r="F18" s="77"/>
+    </row>
+    <row r="19" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A19" s="83" t="s">
         <v>35</v>
       </c>
-      <c r="B19" s="34" t="s">
+      <c r="B19" s="81" t="s">
         <v>34</v>
       </c>
       <c r="C19" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D19" s="49"/>
-      <c r="E19" s="58" t="s">
-        <v>58</v>
-      </c>
-      <c r="F19" s="72" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A20" s="37"/>
-      <c r="B20" s="35"/>
+      <c r="D19" s="67"/>
+      <c r="E19" s="68" t="s">
+        <v>57</v>
+      </c>
+      <c r="F19" s="76" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A20" s="84"/>
+      <c r="B20" s="82"/>
       <c r="C20" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="D20" s="31" t="s">
-        <v>38</v>
-      </c>
-      <c r="E20" s="59"/>
-      <c r="F20" s="73"/>
-    </row>
-    <row r="21" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="D20" s="78" t="s">
+        <v>74</v>
+      </c>
+      <c r="E20" s="69"/>
+      <c r="F20" s="77"/>
+    </row>
+    <row r="21" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A21" s="24"/>
       <c r="B21" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C21" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="D21" s="32"/>
-      <c r="E21" s="60"/>
-      <c r="F21" s="65"/>
-    </row>
-    <row r="22" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="D21" s="79"/>
+      <c r="E21" s="36"/>
+      <c r="F21" s="46" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A22" s="24" t="s">
         <v>36</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C22" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D22" s="80"/>
+      <c r="E22" s="36" t="s">
+        <v>71</v>
+      </c>
+      <c r="F22" s="41" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A23" s="43" t="s">
+        <v>76</v>
+      </c>
+      <c r="B23" s="44" t="s">
+        <v>77</v>
+      </c>
+      <c r="C23" s="45" t="s">
+        <v>79</v>
+      </c>
+      <c r="D23" s="60" t="s">
+        <v>75</v>
+      </c>
+      <c r="E23" s="62" t="s">
+        <v>80</v>
+      </c>
+      <c r="F23" s="47" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A24" s="43" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="44" t="s">
+        <v>78</v>
+      </c>
+      <c r="C24" s="45" t="s">
+        <v>79</v>
+      </c>
+      <c r="D24" s="61"/>
+      <c r="E24" s="63"/>
+      <c r="F24" s="48"/>
+    </row>
+    <row r="25" spans="1:6" ht="55.5" x14ac:dyDescent="0.45">
+      <c r="A25" s="25" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D22" s="33"/>
-      <c r="E22" s="60" t="s">
+      <c r="C25" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="D25" s="49" t="s">
+        <v>58</v>
+      </c>
+      <c r="E25" s="37"/>
+      <c r="F25" s="42" t="s">
         <v>72</v>
       </c>
-      <c r="F22" s="65" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="56.25" x14ac:dyDescent="0.3">
-      <c r="A23" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="B23" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="C23" s="29" t="s">
+    </row>
+    <row r="26" spans="1:6" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="B26" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="D23" s="38" t="s">
-        <v>59</v>
-      </c>
-      <c r="E23" s="61"/>
-      <c r="F23" s="74" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="B24" s="14" t="s">
+      <c r="C26" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="C24" s="29" t="s">
+      <c r="D26" s="49"/>
+      <c r="E26" s="38"/>
+      <c r="F26" s="41"/>
+    </row>
+    <row r="27" spans="1:6" ht="37" x14ac:dyDescent="0.45">
+      <c r="A27" s="27"/>
+      <c r="B27" s="28"/>
+      <c r="C27" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="D27" s="49"/>
+      <c r="E27" s="39" t="s">
+        <v>55</v>
+      </c>
+      <c r="F27" s="41"/>
+    </row>
+    <row r="28" spans="1:6" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A28" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="D24" s="38"/>
-      <c r="E24" s="62"/>
-      <c r="F24" s="65"/>
-    </row>
-    <row r="25" spans="1:6" ht="37.5" x14ac:dyDescent="0.3">
-      <c r="A25" s="27"/>
-      <c r="B25" s="28"/>
-      <c r="C25" s="29" t="s">
+      <c r="B28" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C28" s="30" t="s">
         <v>50</v>
       </c>
-      <c r="D25" s="38"/>
-      <c r="E25" s="63" t="s">
-        <v>56</v>
-      </c>
-      <c r="F25" s="65"/>
-    </row>
-    <row r="26" spans="1:6" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="B26" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="C26" s="30" t="s">
-        <v>51</v>
-      </c>
-      <c r="D26" s="39"/>
-      <c r="E26" s="64" t="s">
-        <v>55</v>
-      </c>
-      <c r="F26" s="65"/>
-    </row>
-    <row r="27" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="3"/>
+      <c r="D28" s="50"/>
+      <c r="E28" s="40" t="s">
+        <v>54</v>
+      </c>
+      <c r="F28" s="41"/>
+    </row>
+    <row r="29" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B29" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="17">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="D17:D19"/>
     <mergeCell ref="E19:E20"/>
@@ -1570,10 +1660,13 @@
     <mergeCell ref="D20:D22"/>
     <mergeCell ref="B19:B20"/>
     <mergeCell ref="A19:A20"/>
-    <mergeCell ref="D23:D26"/>
+    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="D25:D28"/>
     <mergeCell ref="E5:E8"/>
     <mergeCell ref="D5:D13"/>
     <mergeCell ref="D14:D16"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="E23:E24"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
